--- a/public/tableau_de_synthese_epreuve_e5.xlsx
+++ b/public/tableau_de_synthese_epreuve_e5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaelian/Desktop/portfolio-bts-sio/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaelian/Desktop/Portfolio BTS/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFA2352-C367-D14B-B031-480AE7817B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E243B40D-B1EE-1149-8E3B-8AC95AE511DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,9 +100,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>SESSION 2025</t>
-  </si>
-  <si>
     <t>NOM et prénom : BAUDELET Kaelian</t>
   </si>
   <si>
@@ -496,6 +493,9 @@
   </si>
   <si>
     <t>24/03/2026 au 16/04/2026</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1119,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1175,6 +1175,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1249,27 +1267,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1591,83 +1588,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="31"/>
+    </row>
+    <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="33"/>
+      <c r="H3" s="39"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="A5" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="45" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1690,8 +1687,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="41"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1747,16 +1744,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="A8" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1794,18 +1791,18 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="44" t="s">
-        <v>37</v>
+      <c r="A9" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
+        <v>27</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1843,18 +1840,18 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="44" t="s">
-        <v>38</v>
+      <c r="A10" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="47"/>
+        <v>26</v>
+      </c>
+      <c r="C10" s="21"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="48"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1892,18 +1889,18 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="44" t="s">
-        <v>39</v>
+      <c r="A11" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="47"/>
+        <v>25</v>
+      </c>
+      <c r="C11" s="21"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1941,18 +1938,18 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="44" t="s">
-        <v>40</v>
+      <c r="A12" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="48"/>
+      <c r="H12" s="22"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1990,18 +1987,18 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="44" t="s">
-        <v>41</v>
+      <c r="A13" s="19" t="s">
+        <v>40</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="47"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="48"/>
+      <c r="H13" s="22"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -2039,18 +2036,18 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="44" t="s">
-        <v>42</v>
+      <c r="A14" s="19" t="s">
+        <v>41</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="47"/>
+        <v>30</v>
+      </c>
+      <c r="C14" s="21"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="48"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -2088,18 +2085,18 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="44" t="s">
-        <v>43</v>
+      <c r="A15" s="19" t="s">
+        <v>42</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="47"/>
+        <v>32</v>
+      </c>
+      <c r="C15" s="21"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -2137,18 +2134,18 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="44" t="s">
-        <v>44</v>
+      <c r="A16" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="47"/>
+        <v>31</v>
+      </c>
+      <c r="C16" s="21"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="48"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -2186,18 +2183,18 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="45" t="s">
-        <v>45</v>
+      <c r="A17" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="47"/>
+        <v>49</v>
+      </c>
+      <c r="C17" s="21"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="48"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -2235,18 +2232,18 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="45" t="s">
-        <v>46</v>
+      <c r="A18" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="47"/>
+        <v>51</v>
+      </c>
+      <c r="C18" s="21"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2284,18 +2281,18 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="45" t="s">
-        <v>47</v>
+      <c r="A19" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="47"/>
+        <v>50</v>
+      </c>
+      <c r="C19" s="21"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2333,16 +2330,16 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="24"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="30"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2380,18 +2377,18 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="58" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="46" t="s">
-        <v>48</v>
+      <c r="A21" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="47"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="21"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="48"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2429,16 +2426,16 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="21"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="27"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2476,18 +2473,18 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="58" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="46" t="s">
-        <v>49</v>
+      <c r="A23" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="49"/>
+        <v>33</v>
+      </c>
+      <c r="C23" s="23"/>
       <c r="D23" s="15"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="50"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="24"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
